--- a/astro-site/public/dl/plan-negocio-hamburgueseria/calculadora-carne-patatas-escandallo-hamburgueseria.xlsx
+++ b/astro-site/public/dl/plan-negocio-hamburgueseria/calculadora-carne-patatas-escandallo-hamburgueseria.xlsx
@@ -823,7 +823,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>23.000 € brutos al año + 33 % de cargas ÷ 1.840 h ≈ 16 €/h (un cocinero de cadena gana de 22.000 a 25.000 €). Estimación del kit, editable.</t>
+          <t>22.000 € brutos al año (lo más bajo de un cocinero de cadena, que gana de 22.000 a 25.000 €) + 33 % de cargas ÷ 1.840 h ≈ 16 €/h. Estimación del kit, editable.</t>
         </is>
       </c>
     </row>
@@ -1391,7 +1391,7 @@
     <row r="3" ht="50" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>AVISO FIJO. Acrilamida (Reglamento (UE) 2017/2158): fríe a menos de 175 °C, guarda la patata fresca a más de 6 °C, remójala o escáldala antes de freírla y compara el color con la guía de colores de patatas. Aceite (Orden de 26 de enero de 1989): polares por debajo del 25 %, sin añadir aceite nuevo al baño usado y entregado a un gestor autorizado; la norma no obliga a tener un medidor.</t>
+          <t>AVISO FIJO. Acrilamida (Reglamento (UE) 2017/2158): fríe a menos de 175 °C, guarda la patata fresca a más de 6 °C, remójala o escáldala antes de freírla y compara el color con la guía de colores de patatas. Aceite (Orden de 26 de enero de 1989): polares por debajo del 25 %, nada ajeno al aceite añadido al baño y el usado, a un gestor autorizado; la norma no obliga a tener un medidor.</t>
         </is>
       </c>
     </row>
@@ -3378,7 +3378,7 @@
     <row r="42" ht="66" customHeight="1">
       <c r="A42" s="31" t="inlineStr">
         <is>
-          <t>El food cost de la tabla es el del producto servido en sala. En el pedido para llevar se descuenta la caja; en la plataforma, además, se sube el precio con el recargo y se descuenta la comisión sobre ese precio. El margen se ordena por el de sala. AVISO FIJO: las patatas viajan mal; en la plataforma, envase ventilado o déjalas fuera del pedido de reparto. El menú se calcula con un solo IVA, el de la comida; si vendes mucha bebida, separa las dos bases. Este coste es TEÓRICO: el plan de negocio trabaja con un 28 %%, el lado prudente; la diferencia entre la receta y la caja está explicada en la hoja «Instrucciones».</t>
+          <t>El food cost de la tabla es el del producto servido en sala. En el pedido para llevar se descuenta la caja; en la plataforma, además, se sube el precio con el recargo y se descuenta la comisión sobre ese precio. El margen se ordena por el de sala. AVISO FIJO: las patatas viajan mal; en la plataforma, envase ventilado o déjalas fuera del pedido de reparto. El menú se calcula con un solo IVA, el de la comida; si vendes mucha bebida, separa las dos bases. Este coste es TEÓRICO: el plan de negocio trabaja con un 28 %, el lado prudente; la diferencia entre la receta y la caja está explicada en la hoja «Instrucciones».</t>
         </is>
       </c>
     </row>
@@ -3563,7 +3563,7 @@
     <row r="16" ht="60" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>4. Acrilamida (Reglamento (UE) 2017/2158): fríe a menos de 175 °C, guarda la patata fresca a más de 6 °C, remójala o escáldala antes de freírla y compara el color con la guía de colores de patatas. Aceite (Orden de 26 de enero de 1989): polares por debajo del 25 %, sin añadir aceite nuevo al baño usado y entregado a un gestor autorizado; la norma no obliga a tener un medidor, pero conviene medir.</t>
+          <t>4. Acrilamida (Reglamento (UE) 2017/2158): fríe a menos de 175 °C, guarda la patata fresca a más de 6 °C, remójala o escáldala antes de freírla y compara el color con la guía de colores de patatas. Aceite (Orden de 26 de enero de 1989): polares por debajo del 25 %, nada ajeno al aceite añadido al baño y el usado, a un gestor autorizado; la norma no obliga a tener un medidor, pero conviene medir.</t>
         </is>
       </c>
     </row>
@@ -3626,14 +3626,14 @@
     <row r="28" ht="45" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>El IVA de la comida preparada para consumir en el local, para llevar o a domicilio es el 10 % (Ley 37/1992, art. 91). Las bebidas con azúcares o edulcorantes que salen del local, también las zero, llevan el 21 %: esta calculadora usa un solo IVA, el de la comida. Los importes van sin IVA, salvo el precio de carta.</t>
+          <t>El IVA de la comida preparada para consumir en el local, para llevar o a domicilio es el 10 % (Ley 37/1992, art. 91). La cerveza y los refrescos con azúcares o edulcorantes añadidos que salen del local, también los zero, van al 21 %: esta calculadora usa un solo IVA, el de la comida. Los importes van sin IVA, salvo el precio de carta.</t>
         </is>
       </c>
     </row>
     <row r="29" ht="30" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>Cocción. La norma no fija una cifra para la hamburguesa: la AESAN recomienda 70 °C durante 2 minutos como mínimo, tu APPCC decide el punto crítico con una sonda y la smash fina sale hecha por su grosor.</t>
+          <t>Cocción. La norma no fija una cifra para la hamburguesa: la AESAN recomienda 70 °C o más durante al menos 2 minutos, tu APPCC decide el punto crítico con una sonda y la smash fina sale hecha por su grosor.</t>
         </is>
       </c>
     </row>

--- a/astro-site/public/dl/plan-negocio-hamburgueseria/calculadora-carne-patatas-escandallo-hamburgueseria.xlsx
+++ b/astro-site/public/dl/plan-negocio-hamburgueseria/calculadora-carne-patatas-escandallo-hamburgueseria.xlsx
@@ -618,7 +618,7 @@
     <row r="3" ht="64" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>AVISO FIJO. Carne picada (RD 1021/2022, arts. 4.1, 7.2 y 7.3): comprada picada o picada en el local, se conserva a 2 °C o menos; la bola salada antes de la plancha es un preparado de carne, a 4 °C o menos; la picada en el local es del día y nunca de un día para otro. Nada de carne madurada más de 15 días (Inf26008). Los minutos de limpiar y picar (6) y la merma de cocción no tienen fuente: mídelos.</t>
+          <t>AVISO FIJO. Carne picada (RD 1021/2022, arts. 4.1, 7.2 y 7.3): comprada picada o picada en el local, se conserva a 2 °C o menos; la bola salada antes de la plancha es un preparado de carne, a 4 °C o menos; la picada en el local es del día y nunca de un día para otro. La carne madurada semanas queda fuera del plazo de picado de 6 días desde el sacrificio (15 si es vacuno al vacío) (Inf26008). Los minutos de limpiar y picar (6) y la merma de cocción no tienen fuente: mídelos.</t>
         </is>
       </c>
     </row>
@@ -1258,7 +1258,7 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>RD 1021/2022, arts. 7.2 y 7.3: la carne que picas en el local es del día y nunca de un día para otro; músculo sin recortes, con como máximo 6 días desde el sacrificio o 15 si va envasada al vacío. Nada de carne madurada más de 15 días (Inf26008).</t>
+          <t>RD 1021/2022, arts. 7.2 y 7.3: la carne que picas en el local es del día y nunca de un día para otro; músculo sin recortes, con como máximo 6 días desde el sacrificio o 15 si va envasada al vacío. La carne madurada semanas queda fuera de ese plazo (Inf26008).</t>
         </is>
       </c>
     </row>
@@ -3528,7 +3528,7 @@
     <row r="10" ht="75" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>5. Carne picada (RD 1021/2022, arts. 4.1, 7.2 y 7.3). Comprada picada o picada en el local, se conserva a 2 °C o menos; la bola salada antes de la plancha es un preparado de carne, a 4 °C o menos; la picada en el local es del día y nunca de un día para otro, con músculo sin recortes y como máximo 6 días desde el sacrificio, o 15 si va envasada al vacío. Nada de carne madurada más de 15 días (Inf26008). El desplegable de la hoja es solo un recordatorio: no cambia ningún cálculo.</t>
+          <t>5. Carne picada (RD 1021/2022, arts. 4.1, 7.2 y 7.3). Comprada picada o picada en el local, se conserva a 2 °C o menos; la bola salada antes de la plancha es un preparado de carne, a 4 °C o menos; la picada en el local es del día y nunca de un día para otro, con músculo sin recortes y como máximo 6 días desde el sacrificio, o 15 si va envasada al vacío. La carne madurada semanas queda fuera de ese plazo (Inf26008). El desplegable de la hoja es solo un recordatorio: no cambia ningún cálculo.</t>
         </is>
       </c>
     </row>
